--- a/MASTER_보장분석_엑셀_영구표본.xlsx
+++ b/MASTER_보장분석_엑셀_영구표본.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Windows\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Windows\Desktop\중요\보장분석지\0622\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFF01364-AE13-4879-BEB5-D4BD04103D7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EB7C8D1-D139-4C42-8A84-C11C0BA98C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="보장분석" sheetId="1" r:id="rId1"/>
     <sheet name="법칙" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="128">
   <si>
     <t>합계</t>
   </si>
@@ -427,6 +427,10 @@
       </rPr>
       <t>진단비</t>
     </r>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>허혈성 진단비</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
@@ -585,7 +589,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="48">
+  <borders count="49">
     <border>
       <left/>
       <right/>
@@ -1194,13 +1198,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1455,6 +1470,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1463,23 +1493,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1612,7 +1630,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J89"/>
+  <dimension ref="A1:J90"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="1" max="1" width="6.5" customWidth="1"/>
@@ -1626,8 +1644,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="38.25" customHeight="1">
-      <c r="A1" s="96"/>
-      <c r="B1" s="97"/>
+      <c r="A1" s="90"/>
+      <c r="B1" s="91"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -1640,10 +1658,10 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A2" s="88" t="s">
+      <c r="A2" s="95" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="89"/>
+      <c r="B2" s="96"/>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
@@ -1657,10 +1675,10 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A3" s="86" t="s">
+      <c r="A3" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="87"/>
+      <c r="B3" s="94"/>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -1674,10 +1692,10 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A4" s="86" t="s">
+      <c r="A4" s="93" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="87"/>
+      <c r="B4" s="94"/>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -1691,10 +1709,10 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A5" s="93" t="s">
+      <c r="A5" s="97" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="94"/>
+      <c r="B5" s="98"/>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
       <c r="E5" s="10"/>
@@ -1708,7 +1726,7 @@
       </c>
     </row>
     <row r="6" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A6" s="90" t="s">
+      <c r="A6" s="87" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="13" t="s">
@@ -1727,7 +1745,7 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A7" s="91"/>
+      <c r="A7" s="88"/>
       <c r="B7" s="16" t="s">
         <v>7</v>
       </c>
@@ -1744,7 +1762,7 @@
       </c>
     </row>
     <row r="8" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A8" s="91"/>
+      <c r="A8" s="88"/>
       <c r="B8" s="19" t="s">
         <v>8</v>
       </c>
@@ -1761,7 +1779,7 @@
       </c>
     </row>
     <row r="9" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A9" s="91"/>
+      <c r="A9" s="88"/>
       <c r="B9" s="22" t="s">
         <v>9</v>
       </c>
@@ -1778,7 +1796,7 @@
       </c>
     </row>
     <row r="10" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A10" s="92"/>
+      <c r="A10" s="89"/>
       <c r="B10" s="25" t="s">
         <v>10</v>
       </c>
@@ -1795,7 +1813,7 @@
       </c>
     </row>
     <row r="11" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A11" s="90" t="s">
+      <c r="A11" s="87" t="s">
         <v>11</v>
       </c>
       <c r="B11" s="28" t="s">
@@ -1814,7 +1832,7 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A12" s="91"/>
+      <c r="A12" s="88"/>
       <c r="B12" s="31" t="s">
         <v>13</v>
       </c>
@@ -1831,7 +1849,7 @@
       </c>
     </row>
     <row r="13" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A13" s="91"/>
+      <c r="A13" s="88"/>
       <c r="B13" s="31" t="s">
         <v>14</v>
       </c>
@@ -1848,7 +1866,7 @@
       </c>
     </row>
     <row r="14" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A14" s="92"/>
+      <c r="A14" s="89"/>
       <c r="B14" s="25" t="s">
         <v>15</v>
       </c>
@@ -1865,7 +1883,7 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A15" s="90" t="s">
+      <c r="A15" s="87" t="s">
         <v>16</v>
       </c>
       <c r="B15" s="34" t="s">
@@ -1884,7 +1902,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A16" s="91"/>
+      <c r="A16" s="88"/>
       <c r="B16" s="13" t="s">
         <v>18</v>
       </c>
@@ -1901,7 +1919,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A17" s="91"/>
+      <c r="A17" s="88"/>
       <c r="B17" s="38" t="s">
         <v>19</v>
       </c>
@@ -1918,7 +1936,7 @@
       </c>
     </row>
     <row r="18" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A18" s="91"/>
+      <c r="A18" s="88"/>
       <c r="B18" s="40" t="s">
         <v>20</v>
       </c>
@@ -1935,7 +1953,7 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A19" s="91"/>
+      <c r="A19" s="88"/>
       <c r="B19" s="42" t="s">
         <v>125</v>
       </c>
@@ -1949,7 +1967,7 @@
       <c r="J19" s="24"/>
     </row>
     <row r="20" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A20" s="91"/>
+      <c r="A20" s="88"/>
       <c r="B20" s="42" t="s">
         <v>22</v>
       </c>
@@ -1966,7 +1984,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A21" s="91"/>
+      <c r="A21" s="88"/>
       <c r="B21" s="42" t="s">
         <v>23</v>
       </c>
@@ -1983,7 +2001,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A22" s="91"/>
+      <c r="A22" s="88"/>
       <c r="B22" s="42" t="s">
         <v>21</v>
       </c>
@@ -1997,7 +2015,7 @@
       <c r="J22" s="24"/>
     </row>
     <row r="23" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A23" s="91"/>
+      <c r="A23" s="88"/>
       <c r="B23" s="44" t="s">
         <v>24</v>
       </c>
@@ -2014,7 +2032,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A24" s="91"/>
+      <c r="A24" s="88"/>
       <c r="B24" s="44" t="s">
         <v>25</v>
       </c>
@@ -2031,7 +2049,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A25" s="91"/>
+      <c r="A25" s="88"/>
       <c r="B25" s="44" t="s">
         <v>26</v>
       </c>
@@ -2048,7 +2066,7 @@
       </c>
     </row>
     <row r="26" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A26" s="91"/>
+      <c r="A26" s="88"/>
       <c r="B26" s="44" t="s">
         <v>27</v>
       </c>
@@ -2065,7 +2083,7 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A27" s="91"/>
+      <c r="A27" s="88"/>
       <c r="B27" s="31" t="s">
         <v>28</v>
       </c>
@@ -2082,7 +2100,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A28" s="92"/>
+      <c r="A28" s="89"/>
       <c r="B28" s="25" t="s">
         <v>29</v>
       </c>
@@ -2099,7 +2117,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A29" s="90" t="s">
+      <c r="A29" s="87" t="s">
         <v>30</v>
       </c>
       <c r="B29" s="34" t="s">
@@ -2118,7 +2136,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A30" s="91"/>
+      <c r="A30" s="88"/>
       <c r="B30" s="47" t="s">
         <v>32</v>
       </c>
@@ -2135,7 +2153,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A31" s="91"/>
+      <c r="A31" s="88"/>
       <c r="B31" s="50" t="s">
         <v>33</v>
       </c>
@@ -2152,7 +2170,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A32" s="91"/>
+      <c r="A32" s="88"/>
       <c r="B32" s="52" t="s">
         <v>34</v>
       </c>
@@ -2169,7 +2187,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A33" s="91"/>
+      <c r="A33" s="88"/>
       <c r="B33" s="53" t="s">
         <v>35</v>
       </c>
@@ -2186,7 +2204,7 @@
       </c>
     </row>
     <row r="34" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A34" s="91"/>
+      <c r="A34" s="88"/>
       <c r="B34" s="55" t="s">
         <v>36</v>
       </c>
@@ -2203,7 +2221,7 @@
       </c>
     </row>
     <row r="35" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A35" s="91"/>
+      <c r="A35" s="88"/>
       <c r="B35" s="55" t="s">
         <v>37</v>
       </c>
@@ -2217,7 +2235,7 @@
       <c r="J35" s="33"/>
     </row>
     <row r="36" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A36" s="92"/>
+      <c r="A36" s="89"/>
       <c r="B36" s="57" t="s">
         <v>38</v>
       </c>
@@ -2229,12 +2247,12 @@
       <c r="H36" s="26"/>
       <c r="I36" s="26"/>
       <c r="J36" s="27">
-        <f t="shared" ref="J36:J57" si="1">SUM(C35:I35)</f>
+        <f t="shared" ref="J36:J58" si="1">SUM(C35:I35)</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A37" s="95" t="s">
+      <c r="A37" s="99" t="s">
         <v>39</v>
       </c>
       <c r="B37" s="40" t="s">
@@ -2253,7 +2271,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A38" s="91"/>
+      <c r="A38" s="88"/>
       <c r="B38" s="31" t="s">
         <v>41</v>
       </c>
@@ -2270,7 +2288,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A39" s="91"/>
+      <c r="A39" s="88"/>
       <c r="B39" s="31" t="s">
         <v>42</v>
       </c>
@@ -2287,7 +2305,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A40" s="91"/>
+      <c r="A40" s="88"/>
       <c r="B40" s="40" t="s">
         <v>43</v>
       </c>
@@ -2304,7 +2322,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A41" s="91"/>
+      <c r="A41" s="88"/>
       <c r="B41" s="60" t="s">
         <v>44</v>
       </c>
@@ -2321,113 +2339,113 @@
       </c>
     </row>
     <row r="42" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A42" s="91"/>
-      <c r="B42" s="61" t="s">
+      <c r="A42" s="88"/>
+      <c r="B42" s="69" t="s">
         <v>37</v>
       </c>
-      <c r="C42" s="62"/>
-      <c r="D42" s="62"/>
-      <c r="E42" s="62"/>
-      <c r="F42" s="62"/>
-      <c r="G42" s="62"/>
-      <c r="H42" s="62"/>
-      <c r="I42" s="62"/>
-      <c r="J42" s="63">
+      <c r="C42" s="32"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="32"/>
+      <c r="F42" s="32"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="32"/>
+      <c r="I42" s="32"/>
+      <c r="J42" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A43" s="91"/>
-      <c r="B43" s="13" t="s">
+    <row r="43" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A43" s="88"/>
+      <c r="B43" s="86" t="s">
+        <v>127</v>
+      </c>
+      <c r="C43" s="23"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="23"/>
+      <c r="F43" s="23"/>
+      <c r="G43" s="23"/>
+      <c r="H43" s="23"/>
+      <c r="I43" s="23"/>
+      <c r="J43" s="33">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="17.25" customHeight="1">
+      <c r="A44" s="88"/>
+      <c r="B44" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="C43" s="37"/>
-      <c r="D43" s="37"/>
-      <c r="E43" s="37"/>
-      <c r="F43" s="37"/>
-      <c r="G43" s="37"/>
-      <c r="H43" s="37"/>
-      <c r="I43" s="37"/>
-      <c r="J43" s="15">
+      <c r="C44" s="37"/>
+      <c r="D44" s="37"/>
+      <c r="E44" s="37"/>
+      <c r="F44" s="37"/>
+      <c r="G44" s="37"/>
+      <c r="H44" s="37"/>
+      <c r="I44" s="37"/>
+      <c r="J44" s="15">
+        <f>SUM(C42:I42)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="17.25" customHeight="1">
+      <c r="A45" s="88"/>
+      <c r="B45" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C45" s="17"/>
+      <c r="D45" s="17"/>
+      <c r="E45" s="17"/>
+      <c r="F45" s="17"/>
+      <c r="G45" s="17"/>
+      <c r="H45" s="17"/>
+      <c r="I45" s="17"/>
+      <c r="J45" s="51">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A44" s="91"/>
-      <c r="B44" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="C44" s="17"/>
-      <c r="D44" s="17"/>
-      <c r="E44" s="17"/>
-      <c r="F44" s="17"/>
-      <c r="G44" s="17"/>
-      <c r="H44" s="17"/>
-      <c r="I44" s="17"/>
-      <c r="J44" s="51">
+    <row r="46" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A46" s="89"/>
+      <c r="B46" s="64" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" s="20"/>
+      <c r="D46" s="20"/>
+      <c r="E46" s="20"/>
+      <c r="F46" s="20"/>
+      <c r="G46" s="20"/>
+      <c r="H46" s="20"/>
+      <c r="I46" s="20"/>
+      <c r="J46" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A45" s="92"/>
-      <c r="B45" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="C45" s="20"/>
-      <c r="D45" s="20"/>
-      <c r="E45" s="20"/>
-      <c r="F45" s="20"/>
-      <c r="G45" s="20"/>
-      <c r="H45" s="20"/>
-      <c r="I45" s="20"/>
-      <c r="J45" s="21">
+    <row r="47" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A47" s="87" t="s">
+        <v>47</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C47" s="29"/>
+      <c r="D47" s="29"/>
+      <c r="E47" s="29"/>
+      <c r="F47" s="29"/>
+      <c r="G47" s="29"/>
+      <c r="H47" s="29"/>
+      <c r="I47" s="29"/>
+      <c r="J47" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A46" s="90" t="s">
-        <v>47</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C46" s="29"/>
-      <c r="D46" s="29"/>
-      <c r="E46" s="29"/>
-      <c r="F46" s="29"/>
-      <c r="G46" s="29"/>
-      <c r="H46" s="29"/>
-      <c r="I46" s="29"/>
-      <c r="J46" s="30">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A47" s="91"/>
-      <c r="B47" s="65" t="s">
+    <row r="48" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A48" s="88"/>
+      <c r="B48" s="65" t="s">
         <v>49</v>
-      </c>
-      <c r="C47" s="59"/>
-      <c r="D47" s="59"/>
-      <c r="E47" s="59"/>
-      <c r="F47" s="59"/>
-      <c r="G47" s="59"/>
-      <c r="H47" s="59"/>
-      <c r="I47" s="59"/>
-      <c r="J47" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A48" s="91"/>
-      <c r="B48" s="65" t="s">
-        <v>50</v>
       </c>
       <c r="C48" s="59"/>
       <c r="D48" s="59"/>
@@ -2442,26 +2460,26 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A49" s="91"/>
-      <c r="B49" s="60" t="s">
-        <v>51</v>
-      </c>
-      <c r="C49" s="32"/>
-      <c r="D49" s="32"/>
-      <c r="E49" s="32"/>
-      <c r="F49" s="32"/>
-      <c r="G49" s="32"/>
-      <c r="H49" s="32"/>
-      <c r="I49" s="32"/>
+      <c r="A49" s="88"/>
+      <c r="B49" s="65" t="s">
+        <v>50</v>
+      </c>
+      <c r="C49" s="59"/>
+      <c r="D49" s="59"/>
+      <c r="E49" s="59"/>
+      <c r="F49" s="59"/>
+      <c r="G49" s="59"/>
+      <c r="H49" s="59"/>
+      <c r="I49" s="59"/>
       <c r="J49" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A50" s="91"/>
-      <c r="B50" s="31" t="s">
-        <v>52</v>
+      <c r="A50" s="88"/>
+      <c r="B50" s="60" t="s">
+        <v>51</v>
       </c>
       <c r="C50" s="32"/>
       <c r="D50" s="32"/>
@@ -2476,9 +2494,9 @@
       </c>
     </row>
     <row r="51" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A51" s="91"/>
+      <c r="A51" s="88"/>
       <c r="B51" s="31" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C51" s="32"/>
       <c r="D51" s="32"/>
@@ -2493,9 +2511,9 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A52" s="91"/>
-      <c r="B52" s="66" t="s">
-        <v>54</v>
+      <c r="A52" s="88"/>
+      <c r="B52" s="31" t="s">
+        <v>53</v>
       </c>
       <c r="C52" s="32"/>
       <c r="D52" s="32"/>
@@ -2510,9 +2528,9 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A53" s="91"/>
+      <c r="A53" s="88"/>
       <c r="B53" s="66" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C53" s="32"/>
       <c r="D53" s="32"/>
@@ -2526,10 +2544,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A54" s="91"/>
-      <c r="B54" s="31" t="s">
-        <v>56</v>
+    <row r="54" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A54" s="88"/>
+      <c r="B54" s="66" t="s">
+        <v>55</v>
       </c>
       <c r="C54" s="32"/>
       <c r="D54" s="32"/>
@@ -2543,96 +2561,96 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A55" s="92"/>
-      <c r="B55" s="25" t="s">
+    <row r="55" spans="1:10" ht="17.25" customHeight="1">
+      <c r="A55" s="88"/>
+      <c r="B55" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="C55" s="32"/>
+      <c r="D55" s="32"/>
+      <c r="E55" s="32"/>
+      <c r="F55" s="32"/>
+      <c r="G55" s="32"/>
+      <c r="H55" s="32"/>
+      <c r="I55" s="32"/>
+      <c r="J55" s="33">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A56" s="89"/>
+      <c r="B56" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="C55" s="26"/>
-      <c r="D55" s="26"/>
-      <c r="E55" s="26"/>
-      <c r="F55" s="26"/>
-      <c r="G55" s="26"/>
-      <c r="H55" s="26"/>
-      <c r="I55" s="26"/>
-      <c r="J55" s="27">
+      <c r="C56" s="26"/>
+      <c r="D56" s="26"/>
+      <c r="E56" s="26"/>
+      <c r="F56" s="26"/>
+      <c r="G56" s="26"/>
+      <c r="H56" s="26"/>
+      <c r="I56" s="26"/>
+      <c r="J56" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A56" s="98" t="s">
+    <row r="57" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A57" s="92" t="s">
         <v>58</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B57" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C56" s="29"/>
-      <c r="D56" s="29"/>
-      <c r="E56" s="29"/>
-      <c r="F56" s="29"/>
-      <c r="G56" s="29"/>
-      <c r="H56" s="29"/>
-      <c r="I56" s="29"/>
-      <c r="J56" s="30">
+      <c r="C57" s="29"/>
+      <c r="D57" s="29"/>
+      <c r="E57" s="29"/>
+      <c r="F57" s="29"/>
+      <c r="G57" s="29"/>
+      <c r="H57" s="29"/>
+      <c r="I57" s="29"/>
+      <c r="J57" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A57" s="91"/>
-      <c r="B57" s="65" t="s">
+    <row r="58" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A58" s="88"/>
+      <c r="B58" s="65" t="s">
         <v>60</v>
-      </c>
-      <c r="C57" s="59"/>
-      <c r="D57" s="59"/>
-      <c r="E57" s="59"/>
-      <c r="F57" s="59"/>
-      <c r="G57" s="59"/>
-      <c r="H57" s="59"/>
-      <c r="I57" s="59"/>
-      <c r="J57" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A58" s="91"/>
-      <c r="B58" s="60" t="s">
-        <v>61</v>
       </c>
       <c r="C58" s="59"/>
       <c r="D58" s="59"/>
       <c r="E58" s="59"/>
-      <c r="F58" s="68"/>
+      <c r="F58" s="59"/>
       <c r="G58" s="59"/>
       <c r="H58" s="59"/>
       <c r="I58" s="59"/>
-      <c r="J58" s="33" t="s">
+      <c r="J58" s="33">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A59" s="88"/>
+      <c r="B59" s="60" t="s">
+        <v>61</v>
+      </c>
+      <c r="C59" s="59"/>
+      <c r="D59" s="59"/>
+      <c r="E59" s="59"/>
+      <c r="F59" s="68"/>
+      <c r="G59" s="59"/>
+      <c r="H59" s="59"/>
+      <c r="I59" s="59"/>
+      <c r="J59" s="33" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A59" s="91"/>
-      <c r="B59" s="60" t="s">
+    <row r="60" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A60" s="88"/>
+      <c r="B60" s="60" t="s">
         <v>63</v>
-      </c>
-      <c r="C59" s="32"/>
-      <c r="D59" s="32"/>
-      <c r="E59" s="32"/>
-      <c r="F59" s="32"/>
-      <c r="G59" s="32"/>
-      <c r="H59" s="32"/>
-      <c r="I59" s="32"/>
-      <c r="J59" s="33">
-        <f>SUM(C58:I58)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A60" s="91"/>
-      <c r="B60" s="60" t="s">
-        <v>64</v>
       </c>
       <c r="C60" s="32"/>
       <c r="D60" s="32"/>
@@ -2646,10 +2664,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A61" s="91"/>
-      <c r="B61" s="69" t="s">
-        <v>65</v>
+    <row r="61" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A61" s="88"/>
+      <c r="B61" s="60" t="s">
+        <v>64</v>
       </c>
       <c r="C61" s="32"/>
       <c r="D61" s="32"/>
@@ -2663,77 +2681,77 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A62" s="91"/>
-      <c r="B62" s="57" t="s">
+    <row r="62" spans="1:10" ht="17.25" customHeight="1">
+      <c r="A62" s="88"/>
+      <c r="B62" s="69" t="s">
+        <v>65</v>
+      </c>
+      <c r="C62" s="32"/>
+      <c r="D62" s="32"/>
+      <c r="E62" s="32"/>
+      <c r="F62" s="32"/>
+      <c r="G62" s="32"/>
+      <c r="H62" s="32"/>
+      <c r="I62" s="32"/>
+      <c r="J62" s="33">
+        <f>SUM(C61:I61)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A63" s="88"/>
+      <c r="B63" s="57" t="s">
         <v>66</v>
       </c>
-      <c r="C62" s="26"/>
-      <c r="D62" s="26"/>
-      <c r="E62" s="26"/>
-      <c r="F62" s="26"/>
-      <c r="G62" s="26"/>
-      <c r="H62" s="26"/>
-      <c r="I62" s="26"/>
-      <c r="J62" s="27">
-        <f>SUM(C61:I61)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A63" s="91"/>
-      <c r="B63" s="65" t="s">
+      <c r="C63" s="26"/>
+      <c r="D63" s="26"/>
+      <c r="E63" s="26"/>
+      <c r="F63" s="26"/>
+      <c r="G63" s="26"/>
+      <c r="H63" s="26"/>
+      <c r="I63" s="26"/>
+      <c r="J63" s="27">
+        <f>SUM(C62:I62)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A64" s="88"/>
+      <c r="B64" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="C63" s="59"/>
-      <c r="D63" s="59"/>
-      <c r="E63" s="59"/>
-      <c r="F63" s="59"/>
-      <c r="G63" s="59"/>
-      <c r="H63" s="59"/>
-      <c r="I63" s="70"/>
-      <c r="J63" s="24">
-        <f>SUM(C62:I62)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A64" s="91"/>
-      <c r="B64" s="60" t="s">
+      <c r="C64" s="59"/>
+      <c r="D64" s="59"/>
+      <c r="E64" s="59"/>
+      <c r="F64" s="59"/>
+      <c r="G64" s="59"/>
+      <c r="H64" s="59"/>
+      <c r="I64" s="70"/>
+      <c r="J64" s="24">
+        <f>SUM(C63:I63)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A65" s="88"/>
+      <c r="B65" s="60" t="s">
         <v>68</v>
       </c>
-      <c r="C64" s="32"/>
-      <c r="D64" s="32"/>
-      <c r="E64" s="32"/>
-      <c r="F64" s="71"/>
-      <c r="G64" s="32"/>
-      <c r="H64" s="32"/>
-      <c r="I64" s="32"/>
-      <c r="J64" s="33" t="s">
+      <c r="C65" s="32"/>
+      <c r="D65" s="32"/>
+      <c r="E65" s="32"/>
+      <c r="F65" s="71"/>
+      <c r="G65" s="32"/>
+      <c r="H65" s="32"/>
+      <c r="I65" s="32"/>
+      <c r="J65" s="33" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A65" s="91"/>
-      <c r="B65" s="72" t="s">
+    <row r="66" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A66" s="88"/>
+      <c r="B66" s="72" t="s">
         <v>69</v>
-      </c>
-      <c r="C65" s="62"/>
-      <c r="D65" s="62"/>
-      <c r="E65" s="62"/>
-      <c r="F65" s="62"/>
-      <c r="G65" s="62"/>
-      <c r="H65" s="62"/>
-      <c r="I65" s="62"/>
-      <c r="J65" s="33">
-        <f t="shared" ref="J65:J80" si="2">SUM(C64:I64)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A66" s="91"/>
-      <c r="B66" s="72" t="s">
-        <v>70</v>
       </c>
       <c r="C66" s="62"/>
       <c r="D66" s="62"/>
@@ -2743,14 +2761,14 @@
       <c r="H66" s="62"/>
       <c r="I66" s="62"/>
       <c r="J66" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A67" s="91"/>
+        <f t="shared" ref="J66:J81" si="2">SUM(C65:I65)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A67" s="88"/>
       <c r="B67" s="72" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C67" s="62"/>
       <c r="D67" s="62"/>
@@ -2764,10 +2782,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A68" s="91"/>
-      <c r="B68" s="61" t="s">
-        <v>72</v>
+    <row r="68" spans="1:10" ht="17.25" customHeight="1">
+      <c r="A68" s="88"/>
+      <c r="B68" s="72" t="s">
+        <v>71</v>
       </c>
       <c r="C68" s="62"/>
       <c r="D68" s="62"/>
@@ -2776,85 +2794,85 @@
       <c r="G68" s="62"/>
       <c r="H68" s="62"/>
       <c r="I68" s="62"/>
-      <c r="J68" s="63">
+      <c r="J68" s="33">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A69" s="91"/>
-      <c r="B69" s="73" t="s">
+    <row r="69" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A69" s="88"/>
+      <c r="B69" s="61" t="s">
+        <v>72</v>
+      </c>
+      <c r="C69" s="62"/>
+      <c r="D69" s="62"/>
+      <c r="E69" s="62"/>
+      <c r="F69" s="62"/>
+      <c r="G69" s="62"/>
+      <c r="H69" s="62"/>
+      <c r="I69" s="62"/>
+      <c r="J69" s="63">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="17.25" customHeight="1">
+      <c r="A70" s="88"/>
+      <c r="B70" s="73" t="s">
         <v>73</v>
       </c>
-      <c r="C69" s="35"/>
-      <c r="D69" s="35"/>
-      <c r="E69" s="35"/>
-      <c r="F69" s="35"/>
-      <c r="G69" s="35"/>
-      <c r="H69" s="35"/>
-      <c r="I69" s="35"/>
-      <c r="J69" s="30">
+      <c r="C70" s="35"/>
+      <c r="D70" s="35"/>
+      <c r="E70" s="35"/>
+      <c r="F70" s="35"/>
+      <c r="G70" s="35"/>
+      <c r="H70" s="35"/>
+      <c r="I70" s="35"/>
+      <c r="J70" s="30">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A70" s="91"/>
-      <c r="B70" s="74" t="s">
+    <row r="71" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A71" s="88"/>
+      <c r="B71" s="74" t="s">
         <v>74</v>
       </c>
-      <c r="C70" s="26"/>
-      <c r="D70" s="26"/>
-      <c r="E70" s="26"/>
-      <c r="F70" s="26"/>
-      <c r="G70" s="26"/>
-      <c r="H70" s="26"/>
-      <c r="I70" s="26"/>
-      <c r="J70" s="27">
+      <c r="C71" s="26"/>
+      <c r="D71" s="26"/>
+      <c r="E71" s="26"/>
+      <c r="F71" s="26"/>
+      <c r="G71" s="26"/>
+      <c r="H71" s="26"/>
+      <c r="I71" s="26"/>
+      <c r="J71" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A71" s="90" t="s">
+    <row r="72" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A72" s="87" t="s">
         <v>75</v>
       </c>
-      <c r="B71" s="28" t="s">
+      <c r="B72" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="C71" s="5"/>
-      <c r="D71" s="5"/>
-      <c r="E71" s="5"/>
-      <c r="F71" s="5"/>
-      <c r="G71" s="5"/>
-      <c r="H71" s="5"/>
-      <c r="I71" s="5"/>
-      <c r="J71" s="30">
+      <c r="C72" s="5"/>
+      <c r="D72" s="5"/>
+      <c r="E72" s="5"/>
+      <c r="F72" s="5"/>
+      <c r="G72" s="5"/>
+      <c r="H72" s="5"/>
+      <c r="I72" s="5"/>
+      <c r="J72" s="30">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A72" s="91"/>
-      <c r="B72" s="31" t="s">
+    <row r="73" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A73" s="88"/>
+      <c r="B73" s="31" t="s">
         <v>77</v>
-      </c>
-      <c r="C72" s="46"/>
-      <c r="D72" s="46"/>
-      <c r="E72" s="46"/>
-      <c r="F72" s="46"/>
-      <c r="G72" s="46"/>
-      <c r="H72" s="46"/>
-      <c r="I72" s="46"/>
-      <c r="J72" s="33">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A73" s="91"/>
-      <c r="B73" s="31" t="s">
-        <v>78</v>
       </c>
       <c r="C73" s="46"/>
       <c r="D73" s="46"/>
@@ -2869,9 +2887,9 @@
       </c>
     </row>
     <row r="74" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A74" s="91"/>
-      <c r="B74" s="66" t="s">
-        <v>79</v>
+      <c r="A74" s="88"/>
+      <c r="B74" s="31" t="s">
+        <v>78</v>
       </c>
       <c r="C74" s="46"/>
       <c r="D74" s="46"/>
@@ -2885,10 +2903,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A75" s="91"/>
-      <c r="B75" s="31" t="s">
-        <v>80</v>
+    <row r="75" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A75" s="88"/>
+      <c r="B75" s="66" t="s">
+        <v>79</v>
       </c>
       <c r="C75" s="46"/>
       <c r="D75" s="46"/>
@@ -2902,274 +2920,291 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A76" s="92"/>
-      <c r="B76" s="25" t="s">
+    <row r="76" spans="1:10" ht="17.25" customHeight="1">
+      <c r="A76" s="88"/>
+      <c r="B76" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="C76" s="46"/>
+      <c r="D76" s="46"/>
+      <c r="E76" s="46"/>
+      <c r="F76" s="46"/>
+      <c r="G76" s="46"/>
+      <c r="H76" s="46"/>
+      <c r="I76" s="46"/>
+      <c r="J76" s="33">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A77" s="89"/>
+      <c r="B77" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="C76" s="75"/>
-      <c r="D76" s="75"/>
-      <c r="E76" s="75"/>
-      <c r="F76" s="75"/>
-      <c r="G76" s="75"/>
-      <c r="H76" s="75"/>
-      <c r="I76" s="75"/>
-      <c r="J76" s="27">
+      <c r="C77" s="75"/>
+      <c r="D77" s="75"/>
+      <c r="E77" s="75"/>
+      <c r="F77" s="75"/>
+      <c r="G77" s="75"/>
+      <c r="H77" s="75"/>
+      <c r="I77" s="75"/>
+      <c r="J77" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A77" s="90" t="s">
+    <row r="78" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A78" s="87" t="s">
         <v>82</v>
       </c>
-      <c r="B77" s="65" t="s">
+      <c r="B78" s="65" t="s">
         <v>83</v>
       </c>
-      <c r="C77" s="59"/>
-      <c r="D77" s="59"/>
-      <c r="E77" s="59"/>
-      <c r="F77" s="59"/>
-      <c r="G77" s="59"/>
-      <c r="H77" s="59"/>
-      <c r="I77" s="59"/>
-      <c r="J77" s="24">
+      <c r="C78" s="59"/>
+      <c r="D78" s="59"/>
+      <c r="E78" s="59"/>
+      <c r="F78" s="59"/>
+      <c r="G78" s="59"/>
+      <c r="H78" s="59"/>
+      <c r="I78" s="59"/>
+      <c r="J78" s="24">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A78" s="91"/>
-      <c r="B78" s="60" t="s">
+    <row r="79" spans="1:10" ht="17.25" customHeight="1">
+      <c r="A79" s="88"/>
+      <c r="B79" s="60" t="s">
         <v>84</v>
       </c>
-      <c r="C78" s="32"/>
-      <c r="D78" s="32"/>
-      <c r="E78" s="32"/>
-      <c r="F78" s="32"/>
-      <c r="G78" s="32"/>
-      <c r="H78" s="32"/>
-      <c r="I78" s="32"/>
-      <c r="J78" s="33">
+      <c r="C79" s="32"/>
+      <c r="D79" s="32"/>
+      <c r="E79" s="32"/>
+      <c r="F79" s="32"/>
+      <c r="G79" s="32"/>
+      <c r="H79" s="32"/>
+      <c r="I79" s="32"/>
+      <c r="J79" s="33">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A79" s="92"/>
-      <c r="B79" s="74" t="s">
+    <row r="80" spans="1:10" ht="17.25" customHeight="1">
+      <c r="A80" s="89"/>
+      <c r="B80" s="74" t="s">
         <v>85</v>
       </c>
-      <c r="C79" s="26"/>
-      <c r="D79" s="26"/>
-      <c r="E79" s="26"/>
-      <c r="F79" s="26"/>
-      <c r="G79" s="26"/>
-      <c r="H79" s="26"/>
-      <c r="I79" s="26"/>
-      <c r="J79" s="27">
+      <c r="C80" s="26"/>
+      <c r="D80" s="26"/>
+      <c r="E80" s="26"/>
+      <c r="F80" s="26"/>
+      <c r="G80" s="26"/>
+      <c r="H80" s="26"/>
+      <c r="I80" s="26"/>
+      <c r="J80" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A80" s="58" t="s">
+    <row r="81" spans="1:10" ht="17.25" customHeight="1">
+      <c r="A81" s="58" t="s">
         <v>86</v>
       </c>
-      <c r="B80" s="64" t="s">
+      <c r="B81" s="64" t="s">
         <v>87</v>
       </c>
-      <c r="C80" s="20"/>
-      <c r="D80" s="20"/>
-      <c r="E80" s="20"/>
-      <c r="F80" s="20"/>
-      <c r="G80" s="20"/>
-      <c r="H80" s="20"/>
-      <c r="I80" s="20"/>
-      <c r="J80" s="21">
+      <c r="C81" s="20"/>
+      <c r="D81" s="20"/>
+      <c r="E81" s="20"/>
+      <c r="F81" s="20"/>
+      <c r="G81" s="20"/>
+      <c r="H81" s="20"/>
+      <c r="I81" s="20"/>
+      <c r="J81" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A81" s="67" t="s">
+    <row r="82" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A82" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="B81" s="34" t="s">
+      <c r="B82" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="C81" s="35"/>
-      <c r="D81" s="35"/>
-      <c r="E81" s="35"/>
-      <c r="F81" s="35"/>
-      <c r="G81" s="35"/>
-      <c r="H81" s="35"/>
-      <c r="I81" s="35"/>
-      <c r="J81" s="36"/>
-    </row>
-    <row r="82" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A82" s="90" t="s">
+      <c r="C82" s="35"/>
+      <c r="D82" s="35"/>
+      <c r="E82" s="35"/>
+      <c r="F82" s="35"/>
+      <c r="G82" s="35"/>
+      <c r="H82" s="35"/>
+      <c r="I82" s="35"/>
+      <c r="J82" s="36"/>
+    </row>
+    <row r="83" spans="1:10" ht="17.25" customHeight="1">
+      <c r="A83" s="87" t="s">
         <v>89</v>
       </c>
-      <c r="B82" s="28" t="s">
+      <c r="B83" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="C82" s="29"/>
-      <c r="D82" s="29"/>
-      <c r="E82" s="29"/>
-      <c r="F82" s="29"/>
-      <c r="G82" s="29"/>
-      <c r="H82" s="29"/>
-      <c r="I82" s="29"/>
-      <c r="J82" s="30">
-        <f t="shared" ref="J82:J89" si="3">SUM(C81:I81)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A83" s="92"/>
-      <c r="B83" s="25" t="s">
+      <c r="C83" s="29"/>
+      <c r="D83" s="29"/>
+      <c r="E83" s="29"/>
+      <c r="F83" s="29"/>
+      <c r="G83" s="29"/>
+      <c r="H83" s="29"/>
+      <c r="I83" s="29"/>
+      <c r="J83" s="30">
+        <f t="shared" ref="J83:J90" si="3">SUM(C82:I82)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A84" s="89"/>
+      <c r="B84" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="C83" s="26"/>
-      <c r="D83" s="26"/>
-      <c r="E83" s="26"/>
-      <c r="F83" s="26"/>
-      <c r="G83" s="26"/>
-      <c r="H83" s="26"/>
-      <c r="I83" s="26"/>
-      <c r="J83" s="27">
+      <c r="C84" s="26"/>
+      <c r="D84" s="26"/>
+      <c r="E84" s="26"/>
+      <c r="F84" s="26"/>
+      <c r="G84" s="26"/>
+      <c r="H84" s="26"/>
+      <c r="I84" s="26"/>
+      <c r="J84" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A84" s="90" t="s">
+    <row r="85" spans="1:10" ht="17.25" customHeight="1">
+      <c r="A85" s="87" t="s">
         <v>91</v>
       </c>
-      <c r="B84" s="4" t="s">
+      <c r="B85" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C84" s="29"/>
-      <c r="D84" s="29"/>
-      <c r="E84" s="29"/>
-      <c r="F84" s="29"/>
-      <c r="G84" s="29"/>
-      <c r="H84" s="29"/>
-      <c r="I84" s="29"/>
-      <c r="J84" s="30">
+      <c r="C85" s="29"/>
+      <c r="D85" s="29"/>
+      <c r="E85" s="29"/>
+      <c r="F85" s="29"/>
+      <c r="G85" s="29"/>
+      <c r="H85" s="29"/>
+      <c r="I85" s="29"/>
+      <c r="J85" s="30">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A85" s="92"/>
-      <c r="B85" s="57" t="s">
+    <row r="86" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A86" s="89"/>
+      <c r="B86" s="57" t="s">
         <v>93</v>
       </c>
-      <c r="C85" s="26"/>
-      <c r="D85" s="26"/>
-      <c r="E85" s="26"/>
-      <c r="F85" s="26"/>
-      <c r="G85" s="26"/>
-      <c r="H85" s="26"/>
-      <c r="I85" s="26"/>
-      <c r="J85" s="27">
+      <c r="C86" s="26"/>
+      <c r="D86" s="26"/>
+      <c r="E86" s="26"/>
+      <c r="F86" s="26"/>
+      <c r="G86" s="26"/>
+      <c r="H86" s="26"/>
+      <c r="I86" s="26"/>
+      <c r="J86" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A86" s="90" t="s">
+    <row r="87" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A87" s="87" t="s">
         <v>94</v>
       </c>
-      <c r="B86" s="4" t="s">
+      <c r="B87" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C86" s="76"/>
-      <c r="D86" s="76"/>
-      <c r="E86" s="76"/>
-      <c r="F86" s="76"/>
-      <c r="G86" s="76"/>
-      <c r="H86" s="76"/>
-      <c r="I86" s="76"/>
-      <c r="J86" s="30">
+      <c r="C87" s="76"/>
+      <c r="D87" s="76"/>
+      <c r="E87" s="76"/>
+      <c r="F87" s="76"/>
+      <c r="G87" s="76"/>
+      <c r="H87" s="76"/>
+      <c r="I87" s="76"/>
+      <c r="J87" s="30">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A87" s="91"/>
-      <c r="B87" s="60" t="s">
+    <row r="88" spans="1:10" ht="17.25" customHeight="1">
+      <c r="A88" s="88"/>
+      <c r="B88" s="60" t="s">
         <v>96</v>
       </c>
-      <c r="C87" s="77"/>
-      <c r="D87" s="77"/>
-      <c r="E87" s="77"/>
-      <c r="F87" s="77"/>
-      <c r="G87" s="77"/>
-      <c r="H87" s="77"/>
-      <c r="I87" s="77"/>
-      <c r="J87" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A88" s="92"/>
-      <c r="B88" s="22" t="s">
-        <v>97</v>
-      </c>
-      <c r="C88" s="23"/>
-      <c r="D88" s="23"/>
-      <c r="E88" s="23"/>
-      <c r="F88" s="23"/>
-      <c r="G88" s="23"/>
-      <c r="H88" s="23"/>
-      <c r="I88" s="78"/>
+      <c r="C88" s="77"/>
+      <c r="D88" s="77"/>
+      <c r="E88" s="77"/>
+      <c r="F88" s="77"/>
+      <c r="G88" s="77"/>
+      <c r="H88" s="77"/>
+      <c r="I88" s="77"/>
       <c r="J88" s="33">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:10">
-      <c r="A89" s="12" t="s">
+    <row r="89" spans="1:10" ht="17.25" customHeight="1">
+      <c r="A89" s="89"/>
+      <c r="B89" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="C89" s="23"/>
+      <c r="D89" s="23"/>
+      <c r="E89" s="23"/>
+      <c r="F89" s="23"/>
+      <c r="G89" s="23"/>
+      <c r="H89" s="23"/>
+      <c r="I89" s="78"/>
+      <c r="J89" s="33">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10">
+      <c r="A90" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="B89" s="79" t="s">
+      <c r="B90" s="79" t="s">
         <v>99</v>
       </c>
-      <c r="C89" s="80"/>
-      <c r="D89" s="80"/>
-      <c r="E89" s="80"/>
-      <c r="F89" s="80"/>
-      <c r="G89" s="80"/>
-      <c r="H89" s="80"/>
-      <c r="I89" s="80"/>
-      <c r="J89" s="81">
+      <c r="C90" s="80"/>
+      <c r="D90" s="80"/>
+      <c r="E90" s="80"/>
+      <c r="F90" s="80"/>
+      <c r="G90" s="80"/>
+      <c r="H90" s="80"/>
+      <c r="I90" s="80"/>
+      <c r="J90" s="81">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="A86:A88"/>
+    <mergeCell ref="A37:A46"/>
+    <mergeCell ref="A15:A28"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="A87:A89"/>
     <mergeCell ref="A11:A14"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="A46:A55"/>
-    <mergeCell ref="A56:A70"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="A47:A56"/>
+    <mergeCell ref="A57:A71"/>
     <mergeCell ref="A29:A36"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A6:A10"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A71:A76"/>
-    <mergeCell ref="A77:A79"/>
+    <mergeCell ref="A72:A77"/>
+    <mergeCell ref="A78:A80"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A37:A45"/>
-    <mergeCell ref="A15:A28"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/MASTER_보장분석_엑셀_영구표본.xlsx
+++ b/MASTER_보장분석_엑셀_영구표본.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Windows\Desktop\중요\보장분석지\0622\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Windows\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EB7C8D1-D139-4C42-8A84-C11C0BA98C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFF01364-AE13-4879-BEB5-D4BD04103D7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="보장분석" sheetId="1" r:id="rId1"/>
     <sheet name="법칙" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="127">
   <si>
     <t>합계</t>
   </si>
@@ -427,10 +427,6 @@
       </rPr>
       <t>진단비</t>
     </r>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>허혈성 진단비</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
@@ -589,7 +585,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="49">
+  <borders count="48">
     <border>
       <left/>
       <right/>
@@ -1198,24 +1194,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1470,34 +1455,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1630,7 +1612,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J90"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="1" max="1" width="6.5" customWidth="1"/>
@@ -1644,8 +1626,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="38.25" customHeight="1">
-      <c r="A1" s="90"/>
-      <c r="B1" s="91"/>
+      <c r="A1" s="96"/>
+      <c r="B1" s="97"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -1658,10 +1640,10 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A2" s="95" t="s">
+      <c r="A2" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="96"/>
+      <c r="B2" s="89"/>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
@@ -1675,10 +1657,10 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="86" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="94"/>
+      <c r="B3" s="87"/>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -1692,10 +1674,10 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A4" s="93" t="s">
+      <c r="A4" s="86" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="94"/>
+      <c r="B4" s="87"/>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -1709,10 +1691,10 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A5" s="97" t="s">
+      <c r="A5" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="98"/>
+      <c r="B5" s="94"/>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
       <c r="E5" s="10"/>
@@ -1726,7 +1708,7 @@
       </c>
     </row>
     <row r="6" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A6" s="87" t="s">
+      <c r="A6" s="90" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="13" t="s">
@@ -1745,7 +1727,7 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A7" s="88"/>
+      <c r="A7" s="91"/>
       <c r="B7" s="16" t="s">
         <v>7</v>
       </c>
@@ -1762,7 +1744,7 @@
       </c>
     </row>
     <row r="8" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A8" s="88"/>
+      <c r="A8" s="91"/>
       <c r="B8" s="19" t="s">
         <v>8</v>
       </c>
@@ -1779,7 +1761,7 @@
       </c>
     </row>
     <row r="9" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A9" s="88"/>
+      <c r="A9" s="91"/>
       <c r="B9" s="22" t="s">
         <v>9</v>
       </c>
@@ -1796,7 +1778,7 @@
       </c>
     </row>
     <row r="10" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A10" s="89"/>
+      <c r="A10" s="92"/>
       <c r="B10" s="25" t="s">
         <v>10</v>
       </c>
@@ -1813,7 +1795,7 @@
       </c>
     </row>
     <row r="11" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A11" s="87" t="s">
+      <c r="A11" s="90" t="s">
         <v>11</v>
       </c>
       <c r="B11" s="28" t="s">
@@ -1832,7 +1814,7 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A12" s="88"/>
+      <c r="A12" s="91"/>
       <c r="B12" s="31" t="s">
         <v>13</v>
       </c>
@@ -1849,7 +1831,7 @@
       </c>
     </row>
     <row r="13" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A13" s="88"/>
+      <c r="A13" s="91"/>
       <c r="B13" s="31" t="s">
         <v>14</v>
       </c>
@@ -1866,7 +1848,7 @@
       </c>
     </row>
     <row r="14" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A14" s="89"/>
+      <c r="A14" s="92"/>
       <c r="B14" s="25" t="s">
         <v>15</v>
       </c>
@@ -1883,7 +1865,7 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A15" s="87" t="s">
+      <c r="A15" s="90" t="s">
         <v>16</v>
       </c>
       <c r="B15" s="34" t="s">
@@ -1902,7 +1884,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A16" s="88"/>
+      <c r="A16" s="91"/>
       <c r="B16" s="13" t="s">
         <v>18</v>
       </c>
@@ -1919,7 +1901,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A17" s="88"/>
+      <c r="A17" s="91"/>
       <c r="B17" s="38" t="s">
         <v>19</v>
       </c>
@@ -1936,7 +1918,7 @@
       </c>
     </row>
     <row r="18" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A18" s="88"/>
+      <c r="A18" s="91"/>
       <c r="B18" s="40" t="s">
         <v>20</v>
       </c>
@@ -1953,7 +1935,7 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A19" s="88"/>
+      <c r="A19" s="91"/>
       <c r="B19" s="42" t="s">
         <v>125</v>
       </c>
@@ -1967,7 +1949,7 @@
       <c r="J19" s="24"/>
     </row>
     <row r="20" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A20" s="88"/>
+      <c r="A20" s="91"/>
       <c r="B20" s="42" t="s">
         <v>22</v>
       </c>
@@ -1984,7 +1966,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A21" s="88"/>
+      <c r="A21" s="91"/>
       <c r="B21" s="42" t="s">
         <v>23</v>
       </c>
@@ -2001,7 +1983,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A22" s="88"/>
+      <c r="A22" s="91"/>
       <c r="B22" s="42" t="s">
         <v>21</v>
       </c>
@@ -2015,7 +1997,7 @@
       <c r="J22" s="24"/>
     </row>
     <row r="23" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A23" s="88"/>
+      <c r="A23" s="91"/>
       <c r="B23" s="44" t="s">
         <v>24</v>
       </c>
@@ -2032,7 +2014,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A24" s="88"/>
+      <c r="A24" s="91"/>
       <c r="B24" s="44" t="s">
         <v>25</v>
       </c>
@@ -2049,7 +2031,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A25" s="88"/>
+      <c r="A25" s="91"/>
       <c r="B25" s="44" t="s">
         <v>26</v>
       </c>
@@ -2066,7 +2048,7 @@
       </c>
     </row>
     <row r="26" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A26" s="88"/>
+      <c r="A26" s="91"/>
       <c r="B26" s="44" t="s">
         <v>27</v>
       </c>
@@ -2083,7 +2065,7 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A27" s="88"/>
+      <c r="A27" s="91"/>
       <c r="B27" s="31" t="s">
         <v>28</v>
       </c>
@@ -2100,7 +2082,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A28" s="89"/>
+      <c r="A28" s="92"/>
       <c r="B28" s="25" t="s">
         <v>29</v>
       </c>
@@ -2117,7 +2099,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A29" s="87" t="s">
+      <c r="A29" s="90" t="s">
         <v>30</v>
       </c>
       <c r="B29" s="34" t="s">
@@ -2136,7 +2118,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A30" s="88"/>
+      <c r="A30" s="91"/>
       <c r="B30" s="47" t="s">
         <v>32</v>
       </c>
@@ -2153,7 +2135,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A31" s="88"/>
+      <c r="A31" s="91"/>
       <c r="B31" s="50" t="s">
         <v>33</v>
       </c>
@@ -2170,7 +2152,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A32" s="88"/>
+      <c r="A32" s="91"/>
       <c r="B32" s="52" t="s">
         <v>34</v>
       </c>
@@ -2187,7 +2169,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A33" s="88"/>
+      <c r="A33" s="91"/>
       <c r="B33" s="53" t="s">
         <v>35</v>
       </c>
@@ -2204,7 +2186,7 @@
       </c>
     </row>
     <row r="34" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A34" s="88"/>
+      <c r="A34" s="91"/>
       <c r="B34" s="55" t="s">
         <v>36</v>
       </c>
@@ -2221,7 +2203,7 @@
       </c>
     </row>
     <row r="35" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A35" s="88"/>
+      <c r="A35" s="91"/>
       <c r="B35" s="55" t="s">
         <v>37</v>
       </c>
@@ -2235,7 +2217,7 @@
       <c r="J35" s="33"/>
     </row>
     <row r="36" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A36" s="89"/>
+      <c r="A36" s="92"/>
       <c r="B36" s="57" t="s">
         <v>38</v>
       </c>
@@ -2247,12 +2229,12 @@
       <c r="H36" s="26"/>
       <c r="I36" s="26"/>
       <c r="J36" s="27">
-        <f t="shared" ref="J36:J58" si="1">SUM(C35:I35)</f>
+        <f t="shared" ref="J36:J57" si="1">SUM(C35:I35)</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A37" s="99" t="s">
+      <c r="A37" s="95" t="s">
         <v>39</v>
       </c>
       <c r="B37" s="40" t="s">
@@ -2271,7 +2253,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A38" s="88"/>
+      <c r="A38" s="91"/>
       <c r="B38" s="31" t="s">
         <v>41</v>
       </c>
@@ -2288,7 +2270,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A39" s="88"/>
+      <c r="A39" s="91"/>
       <c r="B39" s="31" t="s">
         <v>42</v>
       </c>
@@ -2305,7 +2287,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A40" s="88"/>
+      <c r="A40" s="91"/>
       <c r="B40" s="40" t="s">
         <v>43</v>
       </c>
@@ -2322,7 +2304,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A41" s="88"/>
+      <c r="A41" s="91"/>
       <c r="B41" s="60" t="s">
         <v>44</v>
       </c>
@@ -2339,113 +2321,113 @@
       </c>
     </row>
     <row r="42" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A42" s="88"/>
-      <c r="B42" s="69" t="s">
+      <c r="A42" s="91"/>
+      <c r="B42" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="C42" s="32"/>
-      <c r="D42" s="32"/>
-      <c r="E42" s="32"/>
-      <c r="F42" s="32"/>
-      <c r="G42" s="32"/>
-      <c r="H42" s="32"/>
-      <c r="I42" s="32"/>
-      <c r="J42" s="33">
+      <c r="C42" s="62"/>
+      <c r="D42" s="62"/>
+      <c r="E42" s="62"/>
+      <c r="F42" s="62"/>
+      <c r="G42" s="62"/>
+      <c r="H42" s="62"/>
+      <c r="I42" s="62"/>
+      <c r="J42" s="63">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A43" s="88"/>
-      <c r="B43" s="86" t="s">
-        <v>127</v>
-      </c>
-      <c r="C43" s="23"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="23"/>
-      <c r="F43" s="23"/>
-      <c r="G43" s="23"/>
-      <c r="H43" s="23"/>
-      <c r="I43" s="23"/>
-      <c r="J43" s="33">
+    <row r="43" spans="1:10" ht="17.25" customHeight="1">
+      <c r="A43" s="91"/>
+      <c r="B43" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C43" s="37"/>
+      <c r="D43" s="37"/>
+      <c r="E43" s="37"/>
+      <c r="F43" s="37"/>
+      <c r="G43" s="37"/>
+      <c r="H43" s="37"/>
+      <c r="I43" s="37"/>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A44" s="88"/>
-      <c r="B44" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="C44" s="37"/>
-      <c r="D44" s="37"/>
-      <c r="E44" s="37"/>
-      <c r="F44" s="37"/>
-      <c r="G44" s="37"/>
-      <c r="H44" s="37"/>
-      <c r="I44" s="37"/>
-      <c r="J44" s="15">
-        <f>SUM(C42:I42)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A45" s="88"/>
-      <c r="B45" s="16" t="s">
+      <c r="A44" s="91"/>
+      <c r="B44" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="C45" s="17"/>
-      <c r="D45" s="17"/>
-      <c r="E45" s="17"/>
-      <c r="F45" s="17"/>
-      <c r="G45" s="17"/>
-      <c r="H45" s="17"/>
-      <c r="I45" s="17"/>
-      <c r="J45" s="51">
+      <c r="C44" s="17"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="17"/>
+      <c r="F44" s="17"/>
+      <c r="G44" s="17"/>
+      <c r="H44" s="17"/>
+      <c r="I44" s="17"/>
+      <c r="J44" s="51">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
+    <row r="45" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A45" s="92"/>
+      <c r="B45" s="64" t="s">
+        <v>38</v>
+      </c>
+      <c r="C45" s="20"/>
+      <c r="D45" s="20"/>
+      <c r="E45" s="20"/>
+      <c r="F45" s="20"/>
+      <c r="G45" s="20"/>
+      <c r="H45" s="20"/>
+      <c r="I45" s="20"/>
+      <c r="J45" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
     <row r="46" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A46" s="89"/>
-      <c r="B46" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="C46" s="20"/>
-      <c r="D46" s="20"/>
-      <c r="E46" s="20"/>
-      <c r="F46" s="20"/>
-      <c r="G46" s="20"/>
-      <c r="H46" s="20"/>
-      <c r="I46" s="20"/>
-      <c r="J46" s="21">
+      <c r="A46" s="90" t="s">
+        <v>47</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C46" s="29"/>
+      <c r="D46" s="29"/>
+      <c r="E46" s="29"/>
+      <c r="F46" s="29"/>
+      <c r="G46" s="29"/>
+      <c r="H46" s="29"/>
+      <c r="I46" s="29"/>
+      <c r="J46" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A47" s="87" t="s">
-        <v>47</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C47" s="29"/>
-      <c r="D47" s="29"/>
-      <c r="E47" s="29"/>
-      <c r="F47" s="29"/>
-      <c r="G47" s="29"/>
-      <c r="H47" s="29"/>
-      <c r="I47" s="29"/>
-      <c r="J47" s="30">
+      <c r="A47" s="91"/>
+      <c r="B47" s="65" t="s">
+        <v>49</v>
+      </c>
+      <c r="C47" s="59"/>
+      <c r="D47" s="59"/>
+      <c r="E47" s="59"/>
+      <c r="F47" s="59"/>
+      <c r="G47" s="59"/>
+      <c r="H47" s="59"/>
+      <c r="I47" s="59"/>
+      <c r="J47" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A48" s="88"/>
+      <c r="A48" s="91"/>
       <c r="B48" s="65" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C48" s="59"/>
       <c r="D48" s="59"/>
@@ -2460,26 +2442,26 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A49" s="88"/>
-      <c r="B49" s="65" t="s">
-        <v>50</v>
-      </c>
-      <c r="C49" s="59"/>
-      <c r="D49" s="59"/>
-      <c r="E49" s="59"/>
-      <c r="F49" s="59"/>
-      <c r="G49" s="59"/>
-      <c r="H49" s="59"/>
-      <c r="I49" s="59"/>
+      <c r="A49" s="91"/>
+      <c r="B49" s="60" t="s">
+        <v>51</v>
+      </c>
+      <c r="C49" s="32"/>
+      <c r="D49" s="32"/>
+      <c r="E49" s="32"/>
+      <c r="F49" s="32"/>
+      <c r="G49" s="32"/>
+      <c r="H49" s="32"/>
+      <c r="I49" s="32"/>
       <c r="J49" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A50" s="88"/>
-      <c r="B50" s="60" t="s">
-        <v>51</v>
+      <c r="A50" s="91"/>
+      <c r="B50" s="31" t="s">
+        <v>52</v>
       </c>
       <c r="C50" s="32"/>
       <c r="D50" s="32"/>
@@ -2494,9 +2476,9 @@
       </c>
     </row>
     <row r="51" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A51" s="88"/>
+      <c r="A51" s="91"/>
       <c r="B51" s="31" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C51" s="32"/>
       <c r="D51" s="32"/>
@@ -2511,9 +2493,9 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A52" s="88"/>
-      <c r="B52" s="31" t="s">
-        <v>53</v>
+      <c r="A52" s="91"/>
+      <c r="B52" s="66" t="s">
+        <v>54</v>
       </c>
       <c r="C52" s="32"/>
       <c r="D52" s="32"/>
@@ -2528,9 +2510,9 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A53" s="88"/>
+      <c r="A53" s="91"/>
       <c r="B53" s="66" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C53" s="32"/>
       <c r="D53" s="32"/>
@@ -2544,10 +2526,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A54" s="88"/>
-      <c r="B54" s="66" t="s">
-        <v>55</v>
+    <row r="54" spans="1:10" ht="17.25" customHeight="1">
+      <c r="A54" s="91"/>
+      <c r="B54" s="31" t="s">
+        <v>56</v>
       </c>
       <c r="C54" s="32"/>
       <c r="D54" s="32"/>
@@ -2561,96 +2543,96 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A55" s="88"/>
-      <c r="B55" s="31" t="s">
-        <v>56</v>
-      </c>
-      <c r="C55" s="32"/>
-      <c r="D55" s="32"/>
-      <c r="E55" s="32"/>
-      <c r="F55" s="32"/>
-      <c r="G55" s="32"/>
-      <c r="H55" s="32"/>
-      <c r="I55" s="32"/>
-      <c r="J55" s="33">
+    <row r="55" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A55" s="92"/>
+      <c r="B55" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="C55" s="26"/>
+      <c r="D55" s="26"/>
+      <c r="E55" s="26"/>
+      <c r="F55" s="26"/>
+      <c r="G55" s="26"/>
+      <c r="H55" s="26"/>
+      <c r="I55" s="26"/>
+      <c r="J55" s="27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A56" s="89"/>
-      <c r="B56" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="C56" s="26"/>
-      <c r="D56" s="26"/>
-      <c r="E56" s="26"/>
-      <c r="F56" s="26"/>
-      <c r="G56" s="26"/>
-      <c r="H56" s="26"/>
-      <c r="I56" s="26"/>
-      <c r="J56" s="27">
+      <c r="A56" s="98" t="s">
+        <v>58</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C56" s="29"/>
+      <c r="D56" s="29"/>
+      <c r="E56" s="29"/>
+      <c r="F56" s="29"/>
+      <c r="G56" s="29"/>
+      <c r="H56" s="29"/>
+      <c r="I56" s="29"/>
+      <c r="J56" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A57" s="92" t="s">
-        <v>58</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C57" s="29"/>
-      <c r="D57" s="29"/>
-      <c r="E57" s="29"/>
-      <c r="F57" s="29"/>
-      <c r="G57" s="29"/>
-      <c r="H57" s="29"/>
-      <c r="I57" s="29"/>
-      <c r="J57" s="30">
+      <c r="A57" s="91"/>
+      <c r="B57" s="65" t="s">
+        <v>60</v>
+      </c>
+      <c r="C57" s="59"/>
+      <c r="D57" s="59"/>
+      <c r="E57" s="59"/>
+      <c r="F57" s="59"/>
+      <c r="G57" s="59"/>
+      <c r="H57" s="59"/>
+      <c r="I57" s="59"/>
+      <c r="J57" s="33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A58" s="88"/>
-      <c r="B58" s="65" t="s">
-        <v>60</v>
+      <c r="A58" s="91"/>
+      <c r="B58" s="60" t="s">
+        <v>61</v>
       </c>
       <c r="C58" s="59"/>
       <c r="D58" s="59"/>
       <c r="E58" s="59"/>
-      <c r="F58" s="59"/>
+      <c r="F58" s="68"/>
       <c r="G58" s="59"/>
       <c r="H58" s="59"/>
       <c r="I58" s="59"/>
-      <c r="J58" s="33">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="J58" s="33" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A59" s="88"/>
+      <c r="A59" s="91"/>
       <c r="B59" s="60" t="s">
-        <v>61</v>
-      </c>
-      <c r="C59" s="59"/>
-      <c r="D59" s="59"/>
-      <c r="E59" s="59"/>
-      <c r="F59" s="68"/>
-      <c r="G59" s="59"/>
-      <c r="H59" s="59"/>
-      <c r="I59" s="59"/>
-      <c r="J59" s="33" t="s">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="C59" s="32"/>
+      <c r="D59" s="32"/>
+      <c r="E59" s="32"/>
+      <c r="F59" s="32"/>
+      <c r="G59" s="32"/>
+      <c r="H59" s="32"/>
+      <c r="I59" s="32"/>
+      <c r="J59" s="33">
+        <f>SUM(C58:I58)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A60" s="88"/>
+      <c r="A60" s="91"/>
       <c r="B60" s="60" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C60" s="32"/>
       <c r="D60" s="32"/>
@@ -2664,10 +2646,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A61" s="88"/>
-      <c r="B61" s="60" t="s">
-        <v>64</v>
+    <row r="61" spans="1:10" ht="17.25" customHeight="1">
+      <c r="A61" s="91"/>
+      <c r="B61" s="69" t="s">
+        <v>65</v>
       </c>
       <c r="C61" s="32"/>
       <c r="D61" s="32"/>
@@ -2681,77 +2663,77 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A62" s="88"/>
-      <c r="B62" s="69" t="s">
-        <v>65</v>
-      </c>
-      <c r="C62" s="32"/>
-      <c r="D62" s="32"/>
-      <c r="E62" s="32"/>
-      <c r="F62" s="32"/>
-      <c r="G62" s="32"/>
-      <c r="H62" s="32"/>
-      <c r="I62" s="32"/>
-      <c r="J62" s="33">
+    <row r="62" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A62" s="91"/>
+      <c r="B62" s="57" t="s">
+        <v>66</v>
+      </c>
+      <c r="C62" s="26"/>
+      <c r="D62" s="26"/>
+      <c r="E62" s="26"/>
+      <c r="F62" s="26"/>
+      <c r="G62" s="26"/>
+      <c r="H62" s="26"/>
+      <c r="I62" s="26"/>
+      <c r="J62" s="27">
         <f>SUM(C61:I61)</f>
         <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A63" s="88"/>
-      <c r="B63" s="57" t="s">
-        <v>66</v>
-      </c>
-      <c r="C63" s="26"/>
-      <c r="D63" s="26"/>
-      <c r="E63" s="26"/>
-      <c r="F63" s="26"/>
-      <c r="G63" s="26"/>
-      <c r="H63" s="26"/>
-      <c r="I63" s="26"/>
-      <c r="J63" s="27">
+      <c r="A63" s="91"/>
+      <c r="B63" s="65" t="s">
+        <v>67</v>
+      </c>
+      <c r="C63" s="59"/>
+      <c r="D63" s="59"/>
+      <c r="E63" s="59"/>
+      <c r="F63" s="59"/>
+      <c r="G63" s="59"/>
+      <c r="H63" s="59"/>
+      <c r="I63" s="70"/>
+      <c r="J63" s="24">
         <f>SUM(C62:I62)</f>
         <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A64" s="88"/>
-      <c r="B64" s="65" t="s">
-        <v>67</v>
-      </c>
-      <c r="C64" s="59"/>
-      <c r="D64" s="59"/>
-      <c r="E64" s="59"/>
-      <c r="F64" s="59"/>
-      <c r="G64" s="59"/>
-      <c r="H64" s="59"/>
-      <c r="I64" s="70"/>
-      <c r="J64" s="24">
-        <f>SUM(C63:I63)</f>
-        <v>0</v>
+      <c r="A64" s="91"/>
+      <c r="B64" s="60" t="s">
+        <v>68</v>
+      </c>
+      <c r="C64" s="32"/>
+      <c r="D64" s="32"/>
+      <c r="E64" s="32"/>
+      <c r="F64" s="71"/>
+      <c r="G64" s="32"/>
+      <c r="H64" s="32"/>
+      <c r="I64" s="32"/>
+      <c r="J64" s="33" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A65" s="88"/>
-      <c r="B65" s="60" t="s">
-        <v>68</v>
-      </c>
-      <c r="C65" s="32"/>
-      <c r="D65" s="32"/>
-      <c r="E65" s="32"/>
-      <c r="F65" s="71"/>
-      <c r="G65" s="32"/>
-      <c r="H65" s="32"/>
-      <c r="I65" s="32"/>
-      <c r="J65" s="33" t="s">
-        <v>62</v>
+      <c r="A65" s="91"/>
+      <c r="B65" s="72" t="s">
+        <v>69</v>
+      </c>
+      <c r="C65" s="62"/>
+      <c r="D65" s="62"/>
+      <c r="E65" s="62"/>
+      <c r="F65" s="62"/>
+      <c r="G65" s="62"/>
+      <c r="H65" s="62"/>
+      <c r="I65" s="62"/>
+      <c r="J65" s="33">
+        <f t="shared" ref="J65:J80" si="2">SUM(C64:I64)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A66" s="88"/>
+      <c r="A66" s="91"/>
       <c r="B66" s="72" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C66" s="62"/>
       <c r="D66" s="62"/>
@@ -2761,14 +2743,14 @@
       <c r="H66" s="62"/>
       <c r="I66" s="62"/>
       <c r="J66" s="33">
-        <f t="shared" ref="J66:J81" si="2">SUM(C65:I65)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A67" s="88"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="17.25" customHeight="1">
+      <c r="A67" s="91"/>
       <c r="B67" s="72" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C67" s="62"/>
       <c r="D67" s="62"/>
@@ -2782,10 +2764,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A68" s="88"/>
-      <c r="B68" s="72" t="s">
-        <v>71</v>
+    <row r="68" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A68" s="91"/>
+      <c r="B68" s="61" t="s">
+        <v>72</v>
       </c>
       <c r="C68" s="62"/>
       <c r="D68" s="62"/>
@@ -2794,85 +2776,85 @@
       <c r="G68" s="62"/>
       <c r="H68" s="62"/>
       <c r="I68" s="62"/>
-      <c r="J68" s="33">
+      <c r="J68" s="63">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A69" s="88"/>
-      <c r="B69" s="61" t="s">
-        <v>72</v>
-      </c>
-      <c r="C69" s="62"/>
-      <c r="D69" s="62"/>
-      <c r="E69" s="62"/>
-      <c r="F69" s="62"/>
-      <c r="G69" s="62"/>
-      <c r="H69" s="62"/>
-      <c r="I69" s="62"/>
-      <c r="J69" s="63">
+    <row r="69" spans="1:10" ht="17.25" customHeight="1">
+      <c r="A69" s="91"/>
+      <c r="B69" s="73" t="s">
+        <v>73</v>
+      </c>
+      <c r="C69" s="35"/>
+      <c r="D69" s="35"/>
+      <c r="E69" s="35"/>
+      <c r="F69" s="35"/>
+      <c r="G69" s="35"/>
+      <c r="H69" s="35"/>
+      <c r="I69" s="35"/>
+      <c r="J69" s="30">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A70" s="88"/>
-      <c r="B70" s="73" t="s">
-        <v>73</v>
-      </c>
-      <c r="C70" s="35"/>
-      <c r="D70" s="35"/>
-      <c r="E70" s="35"/>
-      <c r="F70" s="35"/>
-      <c r="G70" s="35"/>
-      <c r="H70" s="35"/>
-      <c r="I70" s="35"/>
-      <c r="J70" s="30">
+    <row r="70" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A70" s="91"/>
+      <c r="B70" s="74" t="s">
+        <v>74</v>
+      </c>
+      <c r="C70" s="26"/>
+      <c r="D70" s="26"/>
+      <c r="E70" s="26"/>
+      <c r="F70" s="26"/>
+      <c r="G70" s="26"/>
+      <c r="H70" s="26"/>
+      <c r="I70" s="26"/>
+      <c r="J70" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A71" s="88"/>
-      <c r="B71" s="74" t="s">
-        <v>74</v>
-      </c>
-      <c r="C71" s="26"/>
-      <c r="D71" s="26"/>
-      <c r="E71" s="26"/>
-      <c r="F71" s="26"/>
-      <c r="G71" s="26"/>
-      <c r="H71" s="26"/>
-      <c r="I71" s="26"/>
-      <c r="J71" s="27">
+      <c r="A71" s="90" t="s">
+        <v>75</v>
+      </c>
+      <c r="B71" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="C71" s="5"/>
+      <c r="D71" s="5"/>
+      <c r="E71" s="5"/>
+      <c r="F71" s="5"/>
+      <c r="G71" s="5"/>
+      <c r="H71" s="5"/>
+      <c r="I71" s="5"/>
+      <c r="J71" s="30">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A72" s="87" t="s">
-        <v>75</v>
-      </c>
-      <c r="B72" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="C72" s="5"/>
-      <c r="D72" s="5"/>
-      <c r="E72" s="5"/>
-      <c r="F72" s="5"/>
-      <c r="G72" s="5"/>
-      <c r="H72" s="5"/>
-      <c r="I72" s="5"/>
-      <c r="J72" s="30">
+      <c r="A72" s="91"/>
+      <c r="B72" s="31" t="s">
+        <v>77</v>
+      </c>
+      <c r="C72" s="46"/>
+      <c r="D72" s="46"/>
+      <c r="E72" s="46"/>
+      <c r="F72" s="46"/>
+      <c r="G72" s="46"/>
+      <c r="H72" s="46"/>
+      <c r="I72" s="46"/>
+      <c r="J72" s="33">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A73" s="88"/>
+      <c r="A73" s="91"/>
       <c r="B73" s="31" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C73" s="46"/>
       <c r="D73" s="46"/>
@@ -2887,9 +2869,9 @@
       </c>
     </row>
     <row r="74" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A74" s="88"/>
-      <c r="B74" s="31" t="s">
-        <v>78</v>
+      <c r="A74" s="91"/>
+      <c r="B74" s="66" t="s">
+        <v>79</v>
       </c>
       <c r="C74" s="46"/>
       <c r="D74" s="46"/>
@@ -2903,10 +2885,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A75" s="88"/>
-      <c r="B75" s="66" t="s">
-        <v>79</v>
+    <row r="75" spans="1:10" ht="17.25" customHeight="1">
+      <c r="A75" s="91"/>
+      <c r="B75" s="31" t="s">
+        <v>80</v>
       </c>
       <c r="C75" s="46"/>
       <c r="D75" s="46"/>
@@ -2920,291 +2902,274 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A76" s="88"/>
-      <c r="B76" s="31" t="s">
-        <v>80</v>
-      </c>
-      <c r="C76" s="46"/>
-      <c r="D76" s="46"/>
-      <c r="E76" s="46"/>
-      <c r="F76" s="46"/>
-      <c r="G76" s="46"/>
-      <c r="H76" s="46"/>
-      <c r="I76" s="46"/>
-      <c r="J76" s="33">
+    <row r="76" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A76" s="92"/>
+      <c r="B76" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="C76" s="75"/>
+      <c r="D76" s="75"/>
+      <c r="E76" s="75"/>
+      <c r="F76" s="75"/>
+      <c r="G76" s="75"/>
+      <c r="H76" s="75"/>
+      <c r="I76" s="75"/>
+      <c r="J76" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A77" s="89"/>
-      <c r="B77" s="25" t="s">
-        <v>81</v>
-      </c>
-      <c r="C77" s="75"/>
-      <c r="D77" s="75"/>
-      <c r="E77" s="75"/>
-      <c r="F77" s="75"/>
-      <c r="G77" s="75"/>
-      <c r="H77" s="75"/>
-      <c r="I77" s="75"/>
-      <c r="J77" s="27">
+      <c r="A77" s="90" t="s">
+        <v>82</v>
+      </c>
+      <c r="B77" s="65" t="s">
+        <v>83</v>
+      </c>
+      <c r="C77" s="59"/>
+      <c r="D77" s="59"/>
+      <c r="E77" s="59"/>
+      <c r="F77" s="59"/>
+      <c r="G77" s="59"/>
+      <c r="H77" s="59"/>
+      <c r="I77" s="59"/>
+      <c r="J77" s="24">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A78" s="87" t="s">
-        <v>82</v>
-      </c>
-      <c r="B78" s="65" t="s">
-        <v>83</v>
-      </c>
-      <c r="C78" s="59"/>
-      <c r="D78" s="59"/>
-      <c r="E78" s="59"/>
-      <c r="F78" s="59"/>
-      <c r="G78" s="59"/>
-      <c r="H78" s="59"/>
-      <c r="I78" s="59"/>
-      <c r="J78" s="24">
+    <row r="78" spans="1:10" ht="17.25" customHeight="1">
+      <c r="A78" s="91"/>
+      <c r="B78" s="60" t="s">
+        <v>84</v>
+      </c>
+      <c r="C78" s="32"/>
+      <c r="D78" s="32"/>
+      <c r="E78" s="32"/>
+      <c r="F78" s="32"/>
+      <c r="G78" s="32"/>
+      <c r="H78" s="32"/>
+      <c r="I78" s="32"/>
+      <c r="J78" s="33">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A79" s="88"/>
-      <c r="B79" s="60" t="s">
-        <v>84</v>
-      </c>
-      <c r="C79" s="32"/>
-      <c r="D79" s="32"/>
-      <c r="E79" s="32"/>
-      <c r="F79" s="32"/>
-      <c r="G79" s="32"/>
-      <c r="H79" s="32"/>
-      <c r="I79" s="32"/>
-      <c r="J79" s="33">
+      <c r="A79" s="92"/>
+      <c r="B79" s="74" t="s">
+        <v>85</v>
+      </c>
+      <c r="C79" s="26"/>
+      <c r="D79" s="26"/>
+      <c r="E79" s="26"/>
+      <c r="F79" s="26"/>
+      <c r="G79" s="26"/>
+      <c r="H79" s="26"/>
+      <c r="I79" s="26"/>
+      <c r="J79" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A80" s="89"/>
-      <c r="B80" s="74" t="s">
-        <v>85</v>
-      </c>
-      <c r="C80" s="26"/>
-      <c r="D80" s="26"/>
-      <c r="E80" s="26"/>
-      <c r="F80" s="26"/>
-      <c r="G80" s="26"/>
-      <c r="H80" s="26"/>
-      <c r="I80" s="26"/>
-      <c r="J80" s="27">
+      <c r="A80" s="58" t="s">
+        <v>86</v>
+      </c>
+      <c r="B80" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="C80" s="20"/>
+      <c r="D80" s="20"/>
+      <c r="E80" s="20"/>
+      <c r="F80" s="20"/>
+      <c r="G80" s="20"/>
+      <c r="H80" s="20"/>
+      <c r="I80" s="20"/>
+      <c r="J80" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A81" s="58" t="s">
-        <v>86</v>
-      </c>
-      <c r="B81" s="64" t="s">
-        <v>87</v>
-      </c>
-      <c r="C81" s="20"/>
-      <c r="D81" s="20"/>
-      <c r="E81" s="20"/>
-      <c r="F81" s="20"/>
-      <c r="G81" s="20"/>
-      <c r="H81" s="20"/>
-      <c r="I81" s="20"/>
-      <c r="J81" s="21">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A82" s="67" t="s">
+    <row r="81" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A81" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="B82" s="34" t="s">
+      <c r="B81" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="C82" s="35"/>
-      <c r="D82" s="35"/>
-      <c r="E82" s="35"/>
-      <c r="F82" s="35"/>
-      <c r="G82" s="35"/>
-      <c r="H82" s="35"/>
-      <c r="I82" s="35"/>
-      <c r="J82" s="36"/>
-    </row>
-    <row r="83" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A83" s="87" t="s">
+      <c r="C81" s="35"/>
+      <c r="D81" s="35"/>
+      <c r="E81" s="35"/>
+      <c r="F81" s="35"/>
+      <c r="G81" s="35"/>
+      <c r="H81" s="35"/>
+      <c r="I81" s="35"/>
+      <c r="J81" s="36"/>
+    </row>
+    <row r="82" spans="1:10" ht="17.25" customHeight="1">
+      <c r="A82" s="90" t="s">
         <v>89</v>
       </c>
-      <c r="B83" s="28" t="s">
+      <c r="B82" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="C83" s="29"/>
-      <c r="D83" s="29"/>
-      <c r="E83" s="29"/>
-      <c r="F83" s="29"/>
-      <c r="G83" s="29"/>
-      <c r="H83" s="29"/>
-      <c r="I83" s="29"/>
-      <c r="J83" s="30">
-        <f t="shared" ref="J83:J90" si="3">SUM(C82:I82)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A84" s="89"/>
-      <c r="B84" s="25" t="s">
+      <c r="C82" s="29"/>
+      <c r="D82" s="29"/>
+      <c r="E82" s="29"/>
+      <c r="F82" s="29"/>
+      <c r="G82" s="29"/>
+      <c r="H82" s="29"/>
+      <c r="I82" s="29"/>
+      <c r="J82" s="30">
+        <f t="shared" ref="J82:J89" si="3">SUM(C81:I81)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A83" s="92"/>
+      <c r="B83" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="C84" s="26"/>
-      <c r="D84" s="26"/>
-      <c r="E84" s="26"/>
-      <c r="F84" s="26"/>
-      <c r="G84" s="26"/>
-      <c r="H84" s="26"/>
-      <c r="I84" s="26"/>
-      <c r="J84" s="27">
+      <c r="C83" s="26"/>
+      <c r="D83" s="26"/>
+      <c r="E83" s="26"/>
+      <c r="F83" s="26"/>
+      <c r="G83" s="26"/>
+      <c r="H83" s="26"/>
+      <c r="I83" s="26"/>
+      <c r="J83" s="27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A85" s="87" t="s">
+    <row r="84" spans="1:10" ht="17.25" customHeight="1">
+      <c r="A84" s="90" t="s">
         <v>91</v>
       </c>
-      <c r="B85" s="4" t="s">
+      <c r="B84" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C85" s="29"/>
-      <c r="D85" s="29"/>
-      <c r="E85" s="29"/>
-      <c r="F85" s="29"/>
-      <c r="G85" s="29"/>
-      <c r="H85" s="29"/>
-      <c r="I85" s="29"/>
-      <c r="J85" s="30">
+      <c r="C84" s="29"/>
+      <c r="D84" s="29"/>
+      <c r="E84" s="29"/>
+      <c r="F84" s="29"/>
+      <c r="G84" s="29"/>
+      <c r="H84" s="29"/>
+      <c r="I84" s="29"/>
+      <c r="J84" s="30">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
+    <row r="85" spans="1:10" ht="16.5" customHeight="1">
+      <c r="A85" s="92"/>
+      <c r="B85" s="57" t="s">
+        <v>93</v>
+      </c>
+      <c r="C85" s="26"/>
+      <c r="D85" s="26"/>
+      <c r="E85" s="26"/>
+      <c r="F85" s="26"/>
+      <c r="G85" s="26"/>
+      <c r="H85" s="26"/>
+      <c r="I85" s="26"/>
+      <c r="J85" s="27">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
     <row r="86" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A86" s="89"/>
-      <c r="B86" s="57" t="s">
-        <v>93</v>
-      </c>
-      <c r="C86" s="26"/>
-      <c r="D86" s="26"/>
-      <c r="E86" s="26"/>
-      <c r="F86" s="26"/>
-      <c r="G86" s="26"/>
-      <c r="H86" s="26"/>
-      <c r="I86" s="26"/>
-      <c r="J86" s="27">
+      <c r="A86" s="90" t="s">
+        <v>94</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C86" s="76"/>
+      <c r="D86" s="76"/>
+      <c r="E86" s="76"/>
+      <c r="F86" s="76"/>
+      <c r="G86" s="76"/>
+      <c r="H86" s="76"/>
+      <c r="I86" s="76"/>
+      <c r="J86" s="30">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A87" s="87" t="s">
-        <v>94</v>
-      </c>
-      <c r="B87" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C87" s="76"/>
-      <c r="D87" s="76"/>
-      <c r="E87" s="76"/>
-      <c r="F87" s="76"/>
-      <c r="G87" s="76"/>
-      <c r="H87" s="76"/>
-      <c r="I87" s="76"/>
-      <c r="J87" s="30">
+    <row r="87" spans="1:10" ht="17.25" customHeight="1">
+      <c r="A87" s="91"/>
+      <c r="B87" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="C87" s="77"/>
+      <c r="D87" s="77"/>
+      <c r="E87" s="77"/>
+      <c r="F87" s="77"/>
+      <c r="G87" s="77"/>
+      <c r="H87" s="77"/>
+      <c r="I87" s="77"/>
+      <c r="J87" s="33">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A88" s="88"/>
-      <c r="B88" s="60" t="s">
-        <v>96</v>
-      </c>
-      <c r="C88" s="77"/>
-      <c r="D88" s="77"/>
-      <c r="E88" s="77"/>
-      <c r="F88" s="77"/>
-      <c r="G88" s="77"/>
-      <c r="H88" s="77"/>
-      <c r="I88" s="77"/>
+      <c r="A88" s="92"/>
+      <c r="B88" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="C88" s="23"/>
+      <c r="D88" s="23"/>
+      <c r="E88" s="23"/>
+      <c r="F88" s="23"/>
+      <c r="G88" s="23"/>
+      <c r="H88" s="23"/>
+      <c r="I88" s="78"/>
       <c r="J88" s="33">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A89" s="89"/>
-      <c r="B89" s="22" t="s">
-        <v>97</v>
-      </c>
-      <c r="C89" s="23"/>
-      <c r="D89" s="23"/>
-      <c r="E89" s="23"/>
-      <c r="F89" s="23"/>
-      <c r="G89" s="23"/>
-      <c r="H89" s="23"/>
-      <c r="I89" s="78"/>
-      <c r="J89" s="33">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10">
-      <c r="A90" s="12" t="s">
+    <row r="89" spans="1:10">
+      <c r="A89" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="B90" s="79" t="s">
+      <c r="B89" s="79" t="s">
         <v>99</v>
       </c>
-      <c r="C90" s="80"/>
-      <c r="D90" s="80"/>
-      <c r="E90" s="80"/>
-      <c r="F90" s="80"/>
-      <c r="G90" s="80"/>
-      <c r="H90" s="80"/>
-      <c r="I90" s="80"/>
-      <c r="J90" s="81">
+      <c r="C89" s="80"/>
+      <c r="D89" s="80"/>
+      <c r="E89" s="80"/>
+      <c r="F89" s="80"/>
+      <c r="G89" s="80"/>
+      <c r="H89" s="80"/>
+      <c r="I89" s="80"/>
+      <c r="J89" s="81">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A37:A46"/>
-    <mergeCell ref="A15:A28"/>
-    <mergeCell ref="A83:A84"/>
-    <mergeCell ref="A87:A89"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="A86:A88"/>
     <mergeCell ref="A11:A14"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="A47:A56"/>
-    <mergeCell ref="A57:A71"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="A46:A55"/>
+    <mergeCell ref="A56:A70"/>
     <mergeCell ref="A29:A36"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A6:A10"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A72:A77"/>
-    <mergeCell ref="A78:A80"/>
+    <mergeCell ref="A71:A76"/>
+    <mergeCell ref="A77:A79"/>
     <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A37:A45"/>
+    <mergeCell ref="A15:A28"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
